--- a/data/trans_bre/P15B_tráfico-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P15B_tráfico-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-14,24</t>
+          <t>-15,48</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-60,11%</t>
+          <t>-61,65%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-36,88; 0,9</t>
+          <t>-37,24; 1,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,78; -3,26</t>
+          <t>-26,8; -3,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 3,84</t>
+          <t>-22,01; 2,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-31,31; -1,21</t>
+          <t>-30,49; -2,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-87,8; 31,77</t>
+          <t>-88,32; 42,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-80,17; -15,14</t>
+          <t>-79,46; -12,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-83,59; 59,79</t>
+          <t>-87,41; 31,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-85,53; -8,2</t>
+          <t>-82,06; -17,97</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 18,06</t>
+          <t>-22,0; 16,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 9,49</t>
+          <t>-12,11; 8,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 14,31</t>
+          <t>-10,6; 14,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 19,67</t>
+          <t>-7,03; 18,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,43; 62,63</t>
+          <t>-55,64; 59,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,63; 43,12</t>
+          <t>-39,42; 43,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,43; 73,77</t>
+          <t>-36,47; 73,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,32; 111,74</t>
+          <t>-27,73; 102,3</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-15,52</t>
+          <t>-12,33</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-38,45%</t>
+          <t>-30,91%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-38,09; 32,58</t>
+          <t>-39,07; 31,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 35,27</t>
+          <t>-16,84; 32,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 11,96</t>
+          <t>-27,88; 13,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-41,2; 6,66</t>
+          <t>-33,73; 12,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-81,51; 235,85</t>
+          <t>-79,76; 218,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,12; 296,26</t>
+          <t>-49,16; 320,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 253,61</t>
+          <t>-90,63; 308,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-71,28; 37,31</t>
+          <t>-64,31; 53,89</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,07</t>
+          <t>-5,36</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-18,86%</t>
+          <t>-19,72%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,91; 1,36</t>
+          <t>-23,19; 0,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 1,44</t>
+          <t>-13,5; 1,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 3,18</t>
+          <t>-13,2; 2,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 4,01</t>
+          <t>-14,67; 3,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,18; 5,14</t>
+          <t>-61,33; 4,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,12; 8,19</t>
+          <t>-47,95; 4,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,11; 18,84</t>
+          <t>-51,08; 17,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,8; 19,67</t>
+          <t>-45,12; 14,95</t>
         </is>
       </c>
     </row>
